--- a/onibusurbano_dados.xlsx
+++ b/onibusurbano_dados.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -439,6 +439,11 @@
           <t>2025-09-16 17:13:03</t>
         </is>
       </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>2025-10-10 12:35:29</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -451,6 +456,11 @@
           <t>Erro</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Erro</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -463,6 +473,11 @@
           <t>4.50</t>
         </is>
       </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -475,6 +490,11 @@
           <t>5.00</t>
         </is>
       </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -487,6 +507,11 @@
           <t>Erro</t>
         </is>
       </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Erro</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -499,6 +524,11 @@
           <t>Erro</t>
         </is>
       </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Erro</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -507,6 +537,11 @@
         </is>
       </c>
       <c r="B7" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
         <is>
           <t>5.00</t>
         </is>

--- a/onibusurbano_dados.xlsx
+++ b/onibusurbano_dados.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -444,6 +444,11 @@
           <t>2025-10-10 12:35:29</t>
         </is>
       </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>2025-11-10 12:37:36</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -461,6 +466,11 @@
           <t>Erro</t>
         </is>
       </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Erro</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -478,6 +488,11 @@
           <t>4.50</t>
         </is>
       </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -495,6 +510,11 @@
           <t>5.00</t>
         </is>
       </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -512,6 +532,11 @@
           <t>Erro</t>
         </is>
       </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Erro</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -529,6 +554,11 @@
           <t>Erro</t>
         </is>
       </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Erro</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -542,6 +572,11 @@
         </is>
       </c>
       <c r="C7" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
         <is>
           <t>5.00</t>
         </is>

--- a/onibusurbano_dados.xlsx
+++ b/onibusurbano_dados.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -449,6 +449,11 @@
           <t>2025-11-10 12:37:36</t>
         </is>
       </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-10 12:39:47</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -471,6 +476,11 @@
           <t>Erro</t>
         </is>
       </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Erro</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -493,6 +503,11 @@
           <t>4.50</t>
         </is>
       </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Erro</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -515,6 +530,11 @@
           <t>5.00</t>
         </is>
       </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -537,6 +557,11 @@
           <t>Erro</t>
         </is>
       </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Erro</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -559,6 +584,11 @@
           <t>Erro</t>
         </is>
       </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Erro</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -577,6 +607,11 @@
         </is>
       </c>
       <c r="D7" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
         <is>
           <t>5.00</t>
         </is>

--- a/onibusurbano_dados.xlsx
+++ b/onibusurbano_dados.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -454,6 +454,11 @@
           <t>2025-12-10 12:39:47</t>
         </is>
       </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-10 12:35:53</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -481,6 +486,11 @@
           <t>Erro</t>
         </is>
       </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Erro</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -508,6 +518,11 @@
           <t>Erro</t>
         </is>
       </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Erro</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -535,6 +550,11 @@
           <t>5.00</t>
         </is>
       </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -562,6 +582,11 @@
           <t>Erro</t>
         </is>
       </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Erro</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -589,6 +614,11 @@
           <t>Erro</t>
         </is>
       </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Erro</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -614,6 +644,11 @@
       <c r="E7" t="inlineStr">
         <is>
           <t>5.00</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>5.30</t>
         </is>
       </c>
     </row>

--- a/onibusurbano_dados.xlsx
+++ b/onibusurbano_dados.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,38 +413,43 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>Cidade</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>2025-09-16 17:13:03</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>2025-10-10 12:35:29</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>2025-11-10 12:37:36</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>2025-12-10 12:39:47</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>2026-01-10 12:35:53</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>2026-02-10 13:07:36</t>
         </is>
       </c>
     </row>
@@ -491,6 +484,11 @@
           <t>Erro</t>
         </is>
       </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Erro</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -523,6 +521,11 @@
           <t>Erro</t>
         </is>
       </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Erro</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -555,6 +558,11 @@
           <t>5.00</t>
         </is>
       </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -587,6 +595,11 @@
           <t>Erro</t>
         </is>
       </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Erro</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -619,6 +632,11 @@
           <t>Erro</t>
         </is>
       </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Erro</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -647,6 +665,11 @@
         </is>
       </c>
       <c r="F7" t="inlineStr">
+        <is>
+          <t>5.30</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
         <is>
           <t>5.30</t>
         </is>

--- a/onibusurbano_dados.xlsx
+++ b/onibusurbano_dados.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,6 +452,11 @@
           <t>2026-02-10 13:07:36</t>
         </is>
       </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>2026-03-10 12:55:37</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -489,6 +494,11 @@
           <t>Erro</t>
         </is>
       </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Erro</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -526,6 +536,11 @@
           <t>Erro</t>
         </is>
       </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Erro</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -563,6 +578,11 @@
           <t>5.00</t>
         </is>
       </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>5.30</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -600,6 +620,11 @@
           <t>Erro</t>
         </is>
       </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Erro</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -637,6 +662,11 @@
           <t>Erro</t>
         </is>
       </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Erro</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -670,6 +700,11 @@
         </is>
       </c>
       <c r="G7" t="inlineStr">
+        <is>
+          <t>5.30</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
         <is>
           <t>5.30</t>
         </is>

--- a/onibusurbano_dados.xlsx
+++ b/onibusurbano_dados.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -457,6 +457,11 @@
           <t>2026-03-10 12:55:37</t>
         </is>
       </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>2026-04-10 13:04:29</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -499,6 +504,11 @@
           <t>Erro</t>
         </is>
       </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Erro</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -541,6 +551,11 @@
           <t>Erro</t>
         </is>
       </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Erro</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -583,6 +598,11 @@
           <t>5.30</t>
         </is>
       </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>5.30</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -625,6 +645,11 @@
           <t>Erro</t>
         </is>
       </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Erro</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -667,6 +692,11 @@
           <t>Erro</t>
         </is>
       </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Erro</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -705,6 +735,11 @@
         </is>
       </c>
       <c r="H7" t="inlineStr">
+        <is>
+          <t>5.30</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
         <is>
           <t>5.30</t>
         </is>

--- a/onibusurbano_dados.xlsx
+++ b/onibusurbano_dados.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -462,6 +462,11 @@
           <t>2026-04-10 13:04:29</t>
         </is>
       </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>2026-05-10 13:10:43</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -509,6 +514,11 @@
           <t>Erro</t>
         </is>
       </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Erro</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -556,6 +566,11 @@
           <t>Erro</t>
         </is>
       </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Erro</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -603,6 +618,11 @@
           <t>5.30</t>
         </is>
       </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>5.30</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -650,6 +670,11 @@
           <t>Erro</t>
         </is>
       </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Erro</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -697,6 +722,11 @@
           <t>Erro</t>
         </is>
       </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Erro</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -740,6 +770,11 @@
         </is>
       </c>
       <c r="I7" t="inlineStr">
+        <is>
+          <t>5.30</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
         <is>
           <t>5.30</t>
         </is>

--- a/onibusurbano_dados.xlsx
+++ b/onibusurbano_dados.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:K7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -467,6 +467,11 @@
           <t>2026-05-10 13:10:43</t>
         </is>
       </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>2026-06-10 15:26:44</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -519,6 +524,11 @@
           <t>Erro</t>
         </is>
       </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Erro</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -571,6 +581,11 @@
           <t>Erro</t>
         </is>
       </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Erro</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -623,6 +638,11 @@
           <t>5.30</t>
         </is>
       </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>5.30</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -675,6 +695,11 @@
           <t>Erro</t>
         </is>
       </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Erro</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -727,6 +752,11 @@
           <t>Erro</t>
         </is>
       </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Erro</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -775,6 +805,11 @@
         </is>
       </c>
       <c r="J7" t="inlineStr">
+        <is>
+          <t>5.30</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
         <is>
           <t>5.30</t>
         </is>

--- a/onibusurbano_dados.xlsx
+++ b/onibusurbano_dados.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K7"/>
+  <dimension ref="A1:L7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -472,6 +472,11 @@
           <t>2026-06-10 15:26:44</t>
         </is>
       </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>2026-07-10 14:15:28</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -529,6 +534,11 @@
           <t>Erro</t>
         </is>
       </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Erro</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -586,6 +596,11 @@
           <t>Erro</t>
         </is>
       </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Erro</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -643,6 +658,11 @@
           <t>5.30</t>
         </is>
       </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>5.30</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -700,6 +720,11 @@
           <t>Erro</t>
         </is>
       </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Erro</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -757,6 +782,11 @@
           <t>Erro</t>
         </is>
       </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Erro</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -810,6 +840,11 @@
         </is>
       </c>
       <c r="K7" t="inlineStr">
+        <is>
+          <t>5.30</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
         <is>
           <t>5.30</t>
         </is>

--- a/onibusurbano_dados.xlsx
+++ b/onibusurbano_dados.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L7"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -477,6 +477,11 @@
           <t>2026-07-10 14:15:28</t>
         </is>
       </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>2026-08-10 12:59:01</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -539,6 +544,11 @@
           <t>Erro</t>
         </is>
       </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Erro</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -601,6 +611,11 @@
           <t>Erro</t>
         </is>
       </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>Erro</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -663,6 +678,11 @@
           <t>5.30</t>
         </is>
       </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>5.30</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -725,6 +745,11 @@
           <t>Erro</t>
         </is>
       </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Erro</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -787,6 +812,11 @@
           <t>Erro</t>
         </is>
       </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>Erro</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -845,6 +875,11 @@
         </is>
       </c>
       <c r="L7" t="inlineStr">
+        <is>
+          <t>5.30</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
         <is>
           <t>5.30</t>
         </is>

--- a/onibusurbano_dados.xlsx
+++ b/onibusurbano_dados.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:N7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -482,6 +482,11 @@
           <t>2026-08-10 12:59:01</t>
         </is>
       </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>2026-09-10 15:46:24</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -549,6 +554,11 @@
           <t>Erro</t>
         </is>
       </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Erro</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -616,6 +626,11 @@
           <t>Erro</t>
         </is>
       </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Erro</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -683,6 +698,11 @@
           <t>5.30</t>
         </is>
       </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>5.30</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -750,6 +770,11 @@
           <t>Erro</t>
         </is>
       </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Erro</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -817,6 +842,11 @@
           <t>Erro</t>
         </is>
       </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Erro</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -880,6 +910,11 @@
         </is>
       </c>
       <c r="M7" t="inlineStr">
+        <is>
+          <t>5.30</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
         <is>
           <t>5.30</t>
         </is>
